--- a/工事担任者問題20261011.xlsx
+++ b/工事担任者問題20261011.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IP-PBXなど|IP-PBXなど 工事担任者,VoIP|VoIP 音声IP 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者,VoIPゲートウェイ|VoIPゲートウェイ アナログ電話 IP変換 PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>IEEE802.3at Type2として標準化されたPoE|IEEE802.3at Type2として標準化されたPoE 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atType2|IEEE802.3atType2 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>ネットワークを構成する機器であるレイヤ3スイッチ|ネットワークを構成する機器であるレイヤ3スイッチ 工事担任者,OSPF|OSPFルーティング 工事担任者,RIP|RIPルーティング 工事担任者</t>
+          <t>レイヤ3スイッチ|レイヤ3スイッチ ルーティング VLAN OSPF RIP 工事担任者,RIPルーティング|RIPルーティング ディスタンスベクタ ホップ数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SPD|SPD サージ防護デバイス 工事担任者,JIS C 5381|JIS C 5381 SPD サージ防護 工事担任者</t>
+          <t>JIS C 5381 SPD規格|JIS C 5381 SPD規格 サージ防護 雷対策 工事担任者,サージ防護|サージ防護 SPD 雷 過電圧 工事担任者,JIS C 5381|JIS C 5381 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10GBASE|10GBASE 工事担任者</t>
+          <t>10GBASE-LR|10GBASE-LR 物理層 64B/66B符号化 シングルモード 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,4B/5B符号化|4B/5B符号化 FDDI 100BASE-TX 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者,スクランブル処理|スクランブル処理 ブロック化 符号化 MAC副層 64B/66B 工事担任者,MAC副層|MAC副層 データリンク層 送信データ ブロック化 工事担任者,同期ヘッダ付加|同期ヘッダ付加 64B/66B 2ビット 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>SS方式 (シングルスター)|SS方式 (シングルスター) 光アクセス 1対1 分岐なし 工事担任者,PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>CATV|CATVシステム 工事担任者,光ファイバ|光ファイバ 工事担任者,同軸ケーブル|同軸ケーブル 工事担任者</t>
+          <t>FTTH|FTTH 光ファイバ 宅内 アクセス 工事担任者,ADSL|ADSL 非対称DSL 電話線 ブロードバンド 工事担任者,VDSL|VDSL 超高速DSL 短距離 マンション 工事担任者,CATVシステム|CATVシステム ヘッドエンド HFC 同軸 工事担任者,CATVヘッドエンド|CATVヘッドエンド 映像配信 信号変換 工事担任者,HFC (光同軸混合網)|HFC (光同軸混合網) CATV 光ファイバ 同軸ケーブル 工事担任者,CATVの光ノード|CATVの光ノード HFC 光-同軸変換 工事担任者,同軸ケーブル|同軸ケーブル CATV HFC インピーダンス 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者,IPv4|IPv4 工事担任者</t>
+          <t>DFビット (Don't Fragment)|DFビット (Don't Fragment) IPv4 フラグメント禁止 ICMPエラー 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS MPLS 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>バッファオーバフロー|バッファオーバフロー攻撃 工事担任者</t>
+          <t>バッファオーバーフロー攻撃|バッファオーバーフロー攻撃 スタック 不正書換 任意プログラム実行 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PPP接続時におけるユーザ認証|PPP接続時におけるユーザ認証 工事担任者,CHAP|CHAP認証 工事担任者,PAP|PAP認証 工事担任者</t>
+          <t>PAP認証|PAP認証 PPP パスワード平文 認証 工事担任者,CHAP認証|CHAP認証 PPP チャレンジ応答 ハッシュ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>ネットワーク利用時における情報漏洩対策|ネットワーク利用時における情報漏洩対策 工事担任者,TLS|TLS暗号化 工事担任者,SMTP|SMTPメールプロトコル 工事担任者</t>
+          <t>情報漏洩対策|情報漏洩対策 セキュリティ 暗号化 TLS スニッフィング 工事担任者,スニッフィング対策|スニッフィング対策 盗聴 暗号化 TLS セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>UDP|UDPプロトコル 工事担任者</t>
+          <t>SNMP|SNMP ネットワーク管理 MIB トラップ 工事担任者,syslog (UNIXシステムログ)|syslog (UNIXシステムログ) セキュリティ 監査ログ リモートホスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ISMS|ISMS 情報セキュリティマネジメント 工事担任者,JIS Q 27001|JIS Q 27001 ISMS 工事担任者</t>
+          <t>ISMS (情報セキュリティマネジメント)|ISMS (情報セキュリティマネジメント) JIS Q 27001 リスク管理 工事担任者,JIS Q 2700|JIS Q 2700 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者,光ファイバ|光ファイバ 工事担任者,プラスチック光ファイバ|プラスチック光ファイバ POF 工事担任者,伝送損失|伝送損失 工事担任者</t>
+          <t>光伝送損失|光伝送損失 パワーバジェット dB/km 工事担任者,プラスチック光ファイバ (POF)|プラスチック光ファイバ (POF) アクリル樹脂 短距離 OITDA 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法|JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>UTP|UTPケーブル 工事担任者,T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OTDR|OTDR 光ファイバ損失 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者,JIS X 5151|JIS X 5151 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>ツイストペアケーブル|ツイストペアケーブル 工事担任者</t>
+          <t>全二重/半二重通信|全二重/半二重通信 イーサネット 衝突 再送処理 CSMA/CD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>工事実施に必要な施工計画書|工事実施に必要な施工計画書 工事担任者</t>
+          <t>施工計画書|施工計画書 現場代理人 受注者 工事着手前 発注者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>図2に示すアローダイアグラム|図2に示すアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者,自営電気通信設備|自営電気通信設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,基礎的電気通信役務|基礎的電気通信役務 ユニバーサルサービス 提供義務 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢端末機器技術基準適合認定｣|電気通信事業法に規定する｢端末機器技術基準適合認定｣ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>工事担任者|工事担任者 資格 法規</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣|工事担任者規則に規定する｢資格者証の再交付｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者,資格者証の書換え交付|資格者証の書換え交付 住所変更 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>有線電気通信法に規定する｢目的｣及び｢設備の検査等｣|有線電気通信法に規定する｢目的｣及び｢設備の検査等｣ 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>分界点|分界点 責任の分界 工事担任者,電気的条件|電気的条件 技術基準 工事担任者,責任の分界|責任の分界 技術基準 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>直流回路|直流回路 アナログ電話 交換設備 2線式 開始終了制御 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>安全性|安全性 技術基準 工事担任者,安全性等|安全性 端末設備 技術基準 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,端末設備の安全性|端末設備の安全性 評価雑音電力 安全 法規 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>｢端末設備内において電波を使用する端末設備｣|｢端末設備内において電波を使用する端末設備｣ 工事担任者</t>
+          <t>端末設備内電波使用 空き状態確認|端末設備内電波使用 空き状態確認 周波数 通信路設定 規則 工事担任者,呼出符号|呼出符号 端末設備 電波使用 規則 告示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>移動電話端末の｢基本的機能｣及び｢発信の機能｣|移動電話端末の｢基本的機能｣及び｢発信の機能｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>｢インターネットプロトコルを使用する専用通信回線設備等端末｣|｢インターネットプロトコルを使用する専用通信回線設備等端末｣ 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>専用通信回線|専用通信回線設備等端末 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する｢架空電線の高さ｣及び｢架空電線の支持物｣|有線電気通信設備令に規定する｢架空電線の高さ｣及び｢架空電線の支持物｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,識別符号|識別符号 アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>64B/66B|64B/66B 伝送路符号化 工事担任者,FEC|FEC 前方誤り訂正 工事担任者,PON|PON 光アクセス 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,XG-PON|XG-PON 次世代PON 光アクセス 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,IEEE802.3avとして標準化され|IEEE802.3avとして標準化され 規格 工事担任者,IEEE802.3avで標準化|IEEE802.3avで標準化 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SIP|SIPプロトコル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>IEEE802.3at Type1として標準化されたPoEの電力クラス0|IEEE802.3at Type1として標準化されたPoEの電力クラス0 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atType1|IEEE802.3atType1 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>無線PAN|無線PAN IEEE802.15 工事担任者</t>
+          <t>Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,OFDM|OFDM 直交周波数分割多重 マルチキャリア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>商用電源を使用するネットワーク機器のノイズ対策に用いられるデバイス|商用電源を使用するネットワーク機器のノイズ対策に用いられるデバイス 工事担任者,インピーダンス|インピーダンス 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>MLT-3|MLT-3 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,VDSL|VDSL 工事担任者,光ファイバ|光ファイバ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,VDSL|VDSL 超高速DSL 短距離 マンション 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者</t>
+          <t>フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>VoIP|VoIP 音声IP 工事担任者</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ アナログ電話 IP変換 PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>広域イーサネット|広域イーサネット 工事担任者,VPN|VPN 工事担任者</t>
+          <t>広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>TCP|TCPプロトコル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>公開鍵暗号及び共通鍵暗号|公開鍵暗号及び共通鍵暗号 工事担任者</t>
+          <t>PKI (公開鍵基盤)|PKI (公開鍵基盤) 電子証明書 CA 認証局 デジタル署名 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>パケットフィルタリング|パケットフィルタリング 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>安全性|安全性 技術基準 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ISMS|ISMS 情報セキュリティマネジメント 工事担任者,JIS Q 27001|JIS Q 27001 ISMS 工事担任者</t>
+          <t>ISMS (情報セキュリティマネジメント)|ISMS (情報セキュリティマネジメント) JIS Q 27001 リスク管理 工事担任者,JIS Q 2700|JIS Q 2700 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atType1|IEEE802.3atType1 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>IPv4|IPv4 工事担任者</t>
+          <t>IPv4|IPv4 パケット フラグメント TTL DFビット 中継ノード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>JIS C 6823:2010光ファイバ損失試験方法における挿入損失法|JIS C 6823:2010光ファイバ損失試験方法における挿入損失法 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>SMTP|SMTP 工事担任者</t>
+          <t>PPP|PPP WAN認証 CHAP PAP LCP 工事担任者,IEEE802.1Dにより標準化されたプロトコルとして|IEEE802.1Dにより標準化されたプロトコルとして 規格 工事担任者,IEEE802.1Dで標準化されたプロトコルはSTP|IEEE802.1Dで標準化されたプロトコルはSTP 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>JIS Q 9024|JIS Q 9024 継続的改善 工事担任者</t>
+          <t>JIS Q 9024|JIS Q 9024 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>工程管理などに用いられるアローダイアグラム|工程管理などに用いられるアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者,端末機器技術基準適合認定|技術基準適合認定 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>工事担任者|工事担任者 資格 法規</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>非常事態における有線電気通信設備の運用|有線電気通信法 非常事態 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>｢絶縁抵抗等｣|｢絶縁抵抗等｣ 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 アクセス制御 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>自営電気通信設備|自営電気通信設備 工事担任者,安全性|安全性 技術基準 工事担任者,安全性等|安全性 端末設備 技術基準 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>制御チャネル|制御チャネル IP電話 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>責任の分界又は安全性等|責任の分界又は安全性等 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末の｢電気的条件等｣|専用通信回線設備等端末の｢電気的条件等｣ 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>インターネットプロトコル電話端末の｢基本的機能｣|インターネットプロトコル電話端末の｢基本的機能｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>IP-PBX及びIPセントレックス|IP-PBX及びIPセントレックス 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>帯域幅|帯域幅 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,MIMO|MIMO 複数アンテナ 空間多重 無線LAN 工事担任者,OFDM|OFDM 直交周波数分割多重 マルチキャリア 工事担任者,IEEE802.11標準の無線LANには|IEEE802.11標準の無線LANには 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>LoRa|LoRaWAN LPWA 工事担任者,LoRaWAN|LoRaWAN LPWA 工事担任者,SIGFOX|SIGFOX LPWA 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>EMC|EMC 電磁両立性 工事担任者,用語|電気通信用語 工事担任者</t>
+          <t>JIS C 6005|JIS C 6005 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>SS方式 (シングルスター)|SS方式 (シングルスター) 光アクセス 1対1 分岐なし 工事担任者,PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>MACアドレスなど|MACアドレスなど 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者,IPv4|IPv4 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS MPLS 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>ICMP|ICMPプロトコル 工事担任者,DoS|DoS攻撃 工事担任者</t>
+          <t>DoS/DDoS攻撃|DoS/DDoS攻撃 サービス妨害 帯域消費 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>PKI(公開鍵基盤)の仕組みなど|PKI(公開鍵基盤)の仕組みなど 工事担任者</t>
+          <t>PKI (公開鍵基盤)|PKI (公開鍵基盤) 電子証明書 CA 認証局 デジタル署名 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>バッファオーバフロー|バッファオーバフロー攻撃 工事担任者</t>
+          <t>バッファオーバーフロー攻撃|バッファオーバーフロー攻撃 スタック 不正書換 任意プログラム実行 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>デフォルト|デフォルト 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>情報セキュリティポリシーに関して望ましいとされている運用方法など|情報セキュリティポリシーに関して望ましいとされている運用方法など 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>JIS C 0303 構内電気設備の配線用図記号|JIS C 0303 配線用図記号 工事担任者</t>
+          <t>JIS C 0303|JIS C 0303 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法|JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>UTP|UTPケーブル 工事担任者,T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>OTDR|OTDR 光ファイバ損失 工事担任者,JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>施工計画、施工管理など|施工計画、施工管理など 工事担任者</t>
+          <t>施工計画書|施工計画書 現場代理人 受注者 工事着手前 発注者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>図2に示すアローダイアグラム|図2に示すアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢工事担任者資格者証｣|電気通信事業法に規定する｢工事担任者資格者証｣ 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢基礎的電気通信役務の提供｣及び｢管理規程｣|電気通信事業法に規定する｢基礎的電気通信役務の提供｣及び｢管理規程｣ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者,基礎的電気通信役務|基礎的電気通信役務 ユニバーサルサービス 提供義務 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣|工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者,管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>鳴音|鳴音防止条件 技術基準 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>｢端末設備内において電波を使用する端末設備｣|｢端末設備内において電波を使用する端末設備｣ 工事担任者</t>
+          <t>端末設備内電波使用 空き状態確認|端末設備内電波使用 空き状態確認 周波数 通信路設定 規則 工事担任者,呼出符号|呼出符号 端末設備 電波使用 規則 告示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14133,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>責任の分界及び安全性等|責任の分界及び安全性等 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>インターネットプロトコル電話|IP電話端末 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14623,7 +14623,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>インターネットプロトコル移動電話端末の｢基本的機能｣及び｢発信の機能｣|インターネットプロトコル移動電話端末の｢基本的機能｣及び｢発信の機能｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>不正アクセス行為の禁止等に関する法律に規定する事項|不正アクセス行為の禁止等に関する法律に規定する事項 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>電子署名及び認証業務に関する法律に規定する用語|電子署名及び認証業務に関する法律に規定する用語 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>64B/66B|64B/66B 伝送路符号化 工事担任者,PON|PON 光アクセス 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,XG-PON|XG-PON 次世代PON 光アクセス 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,IEEE802.3avとして標準化され|IEEE802.3avとして標準化され 規格 工事担任者,IEEE802.3avで標準化|IEEE802.3avで標準化 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>カットアンドスルー|カットアンドスルー 工事担任者</t>
+          <t>IPフラグメント処理|IPフラグメント処理 MTU 分割 IPv4 IPv6 DFビット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,PoE++ (IEEE802.3bt)|PoE++ (IEEE802.3bt) 高電力給電 4ペア 90W 工事担任者,カテゴリ5e UTP|カテゴリ5e UTP ギガビット 100MHz 工事担任者,IEEE802.3btとして標準化されたPoEのType4|IEEE802.3btとして標準化されたPoEのType4 規格 工事担任者,IEEE802.3btType4|IEEE802.3btType4 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>ビーコン|ビーコン 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,無線LANアクセスポイント|無線LANアクセスポイント Wi-Fi SSID BSS 工事担任者,IEEE802.11nとして標準化された無線LAN規格では|IEEE802.11nとして標準化された無線LAN規格では 規格 工事担任者,IEEE802.11nでは複数フレームへの確認応答を1回にまとめて送信するブロックACK|IEEE802.11nでは複数フレームへの確認応答を1回にまとめて送信するブロックACK 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15580,7 +15580,7 @@
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>SPD|SPD サージ防護デバイス 工事担任者,JIS C 5381|JIS C 5381 SPD サージ防護 工事担任者</t>
+          <t>JIS C 5381 SPD規格|JIS C 5381 SPD規格 サージ防護 雷対策 工事担任者,サージ防護|サージ防護 SPD 雷 過電圧 工事担任者,JIS C 5381|JIS C 5381 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>MLT-3|MLT-3 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者</t>
+          <t>SS方式 (シングルスター)|SS方式 (シングルスター) 光アクセス 1対1 分岐なし 工事担任者,PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者,全二重/半二重通信|全二重/半二重通信 イーサネット 衝突 再送処理 CSMA/CD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>オンプレミス|オンプレミス 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>VoIP|VoIP 音声IP 工事担任者</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ アナログ電話 IP変換 PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>広域イーサネットで用いられるEoMPLS|広域イーサネットで用いられるEoMPLS 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>クロスサイトスクリプティング|クロスサイトスクリプティング 工事担任者</t>
+          <t>SQLインジェクション|SQLインジェクション データベース攻撃 Webセキュリティ 工事担任者,クロスサイトスクリプティング (XSS)|クロスサイトスクリプティング (XSS) Webセキュリティ スクリプト注入 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>パスワードによる認証など|パスワードによる認証など 工事担任者</t>
+          <t>PAP認証|PAP認証 PPP パスワード平文 認証 工事担任者,スニッフィング対策|スニッフィング対策 盗聴 暗号化 TLS セキュリティ 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>無線LANのセキュリティ|無線LANのセキュリティ 工事担任者</t>
+          <t>情報漏洩対策|情報漏洩対策 セキュリティ 暗号化 TLS スニッフィング 工事担任者,無線LANアクセスポイント|無線LANアクセスポイント Wi-Fi SSID BSS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>IPsec及びIPsec-VPN|IPsec及びIPsec-VPN 工事担任者</t>
+          <t>IPsec|IPsec VPN 暗号化 トンネル AH ESP IKE 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>アンチパスバック|アンチパスバック 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者,光ファイバ|光ファイバ 工事担任者,プラスチック光ファイバ|プラスチック光ファイバ POF 工事担任者,伝送損失|伝送損失 工事担任者</t>
+          <t>光伝送損失|光伝送損失 パワーバジェット dB/km 工事担任者,プラスチック光ファイバ (POF)|プラスチック光ファイバ (POF) アクリル樹脂 短距離 OITDA 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者,UTP|UTPケーブル 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,100BASE-TX|100BASE-TX ファストイーサネット UTP 工事担任者,カテゴリ5e UTP|カテゴリ5e UTP ギガビット 100MHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>平衡ケーブルを用いたLAN配線のフィールドテストなど|平衡ケーブルを用いたLAN配線のフィールドテストなど 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>施工計画、施工管理など|施工計画、施工管理など 工事担任者</t>
+          <t>施工計画書|施工計画書 現場代理人 受注者 工事着手前 発注者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>図に示すアローダイアグラム|図に示すアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者,重要通信|重要通信 確保 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣|工事担任者規則に規定する｢資格者証の再交付｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者,資格者証の書換え交付|資格者証の書換え交付 住所変更 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>有線電気通信法に規定する｢目的｣及び｢設備の検査等｣|有線電気通信法に規定する｢目的｣及び｢設備の検査等｣ 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18587,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>責任の分界及び安全性等|責任の分界及び安全性等 工事担任者,鳴音|鳴音防止条件 技術基準 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>容易に判別|容易に判別 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>雑音電力の尖頭値|雑音電力の尖頭値 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,端末設備の安全性|端末設備の安全性 評価雑音電力 安全 法規 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>｢配線設備等｣|｢配線設備等｣ 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>漏話|漏話 クロストーク 工事担任者,専用通信回線|専用通信回線設備等端末 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19352,7 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末の｢電気的条件等｣|専用通信回線設備等端末の｢電気的条件等｣ 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>｢インターネットプロトコルを使用する専用通信回線設備等端末｣|｢インターネットプロトコルを使用する専用通信回線設備等端末｣ 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19847,7 +19847,7 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>不正アクセス行為の禁止等に関する法律に規定する｢定義｣|不正アクセス行為の禁止等に関する法律に規定する｢定義｣ 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20132,7 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>IP-PBX|IP-PBX 工事担任者,SIP|SIPプロトコル 工事担任者,TCP|TCPプロトコル 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20225,7 +20225,7 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>IEEE802.3at Type1として標準化されたPoEの電力クラス0|IEEE802.3at Type1として標準化されたPoEの電力クラス0 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atType1|IEEE802.3atType1 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>5G|5G 移動通信 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,IEEE802.11標準の無線LAN規格のうち|IEEE802.11標準の無線LAN規格のうち 規格 工事担任者,IEEE802.11a及びIEEE802|IEEE802.11a及びIEEE802 規格 工事担任者,IEEE802.11n及びIEEE802|IEEE802.11n及びIEEE802 規格 工事担任者,IEEE802.11ac及びIEEE802|IEEE802.11ac及びIEEE802 規格 工事担任者,IEEE802.11nおよびIEEE802|IEEE802.11nおよびIEEE802 規格 工事担任者,IEEE802.11aと802|IEEE802.11aと802 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>ノーマルモード|ノーマルモード 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>10GBASE|10GBASE 工事担任者</t>
+          <t>10GBASE-LR|10GBASE-LR 物理層 64B/66B符号化 シングルモード 工事担任者,1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,4B/5B符号化|4B/5B符号化 FDDI 100BASE-TX 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者,スクランブル処理|スクランブル処理 ブロック化 符号化 MAC副層 64B/66B 工事担任者,MAC副層|MAC副層 データリンク層 送信データ ブロック化 工事担任者,同期ヘッダ付加|同期ヘッダ付加 64B/66B 2ビット 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>CATV|CATVシステム 工事担任者,光ファイバ|光ファイバ 工事担任者,変調|変調方式 工事担任者</t>
+          <t>OFDM|OFDM 直交周波数分割多重 マルチキャリア 工事担任者,CATVシステム|CATVシステム ヘッドエンド HFC 同軸 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者,FDMA|FDMA 周波数分割多元接続 工事担任者,CSMA/CD|CSMA/CD 衝突検出 イーサネット 半二重 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>IEEE802.3aeとして標準化されたLAN用の [_____]|IEEE802.3aeとして標準化されたLAN用の [_____] 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>10GBASE-LR|10GBASE-LR 物理層 64B/66B符号化 シングルモード 工事担任者,10GBASE-SR|10GBASE-SR マルチモード 短距離 工事担任者,10GBASE-ER|10GBASE-ER 長距離 シングルモード 工事担任者,1000BASE-SX|1000BASE-SX ギガビット マルチモード 工事担任者,シングルモードファイバ (SMF)|シングルモードファイバ (SMF) 長距離 低損失 コア 工事担任者,マルチモードファイバ (MMF)|マルチモードファイバ (MMF) 短距離 コア 工事担任者,IEEE802.3aeとして標準化されたLAN用の|IEEE802.3aeとして標準化されたLAN用の 規格 工事担任者,IEEE802.3aeの10GBASE|IEEE802.3aeの10GBASE 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>IETFのRFC4443として標準化されたICMPv6など|IETFのRFC4443として標準化されたICMPv6など 工事担任者,IPv6|IPv6 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS MPLS 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20998,7 +20998,7 @@
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>コンピュータシステムへの脅威など|コンピュータシステムへの脅威など 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>VPN|VPN 工事担任者</t>
+          <t>SSL/TLS|SSL/TLS 暗号化 証明書 HTTPS 工事担任者,IPsec|IPsec VPN 暗号化 トンネル AH ESP IKE 工事担任者,PPP|PPP WAN認証 CHAP PAP LCP 工事担任者,SSH|SSH 暗号化リモートログイン 公開鍵認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21192,7 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>ポートスキャン|ポートスキャン 工事担任者</t>
+          <t>ファイアウォール|ファイアウォール パケットフィルタリング ステートフル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>不正アクセス|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者,DNS|DNS 名前解決 ドメイン IPアドレス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>入退室管理におけるセキュリティ用語など|入退室管理におけるセキュリティ用語など 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6841|JIS C 6841 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>ギガビットイーサネットのLAN配線工事など|ギガビットイーサネットのLAN配線工事など 工事担任者,1000BASE|1000BASE 工事担任者,UTP|UTPケーブル 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,カテゴリ6 UTP|カテゴリ6 UTP ギガビット 250MHz 工事担任者,カテゴリ5e UTP|カテゴリ5e UTP ギガビット 100MHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>UTP|UTPケーブル 工事担任者,T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21972,7 +21972,7 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>HTTP|HTTP 工事担任者</t>
+          <t>PPP|PPP WAN認証 CHAP PAP LCP 工事担任者,IEEE802.1Dにより標準化されたプロトコルとして|IEEE802.1Dにより標準化されたプロトコルとして 規格 工事担任者,IEEE802.1Dで標準化されたプロトコルはSTP|IEEE802.1Dで標準化されたプロトコルはSTP 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>OTDR|OTDR 光ファイバ損失 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者,JIS X 5151|JIS X 5151 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>工事実施に必要な施工計画書|工事実施に必要な施工計画書 工事担任者</t>
+          <t>施工計画書|施工計画書 現場代理人 受注者 工事着手前 発注者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22352,7 +22352,7 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム 工程管理 工事担任者,クリティカルパス|クリティカルパス 工程管理 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢工事担任者資格者証｣|電気通信事業法に規定する｢工事担任者資格者証｣ 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢管理規程｣及び｢技術基準適合命令｣|電気通信事業法に規定する｢管理規程｣及び｢技術基準適合命令｣ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定番号の表示が付されていないものとみなす場合|端末機器の技術基準適合認定番号の表示が付されていないものとみなす場合 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22829,7 +22829,7 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22929,7 +22929,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23028,7 +23028,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の交付｣及び｢資格者証の再交付｣|工事担任者規則に規定する｢資格者証の交付｣及び｢資格者証の再交付｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>非常事態における有線電気通信設備の運用|有線電気通信法 非常事態 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>直流回路|直流回路 アナログ電話 交換設備 2線式 開始終了制御 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>｢責任の分界｣|｢責任の分界｣ 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>｢配線設備等｣|｢配線設備等｣ 工事担任者,絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24106,7 +24106,7 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>電気的条件|電気的条件 技術基準 工事担任者,インターネットプロトコル電話|IP電話端末 工事担任者</t>
+          <t>分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>｢インターネットプロトコルを使用する専用通信回線設備等端末｣|｢インターネットプロトコルを使用する専用通信回線設備等端末｣ 工事担任者,アクセス制御|アクセス制御 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する｢屋内電線｣及び｢有線電気通信設備の保安｣|有線電気通信設備令に規定する｢屋内電線｣及び｢有線電気通信設備の保安｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24486,7 +24486,7 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24575,7 +24575,7 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24667,7 +24667,7 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24759,7 +24759,7 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24847,7 +24847,7 @@
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,光スプリッタ|光スプリッタ PON 光分岐 受動素子 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24947,7 +24947,7 @@
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>IPセントレックスサービス及びIP-PBX|IPセントレックスサービス及びIP-PBX 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>IEEE802.11ax 無線LAN周波数帯|IEEE802.11ax Wi-Fi6 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,IEEE802.11axとして標準化された無線LAN規格において|IEEE802.11axとして標準化された無線LAN規格において 規格 工事担任者,IEEE802.11ax|IEEE802.11ax 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25133,7 +25133,7 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者,ツイストペアケーブル|ツイストペアケーブル 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,PoE++ (IEEE802.3bt)|PoE++ (IEEE802.3bt) 高電力給電 4ペア 90W 工事担任者,カテゴリ5e UTP|カテゴリ5e UTP ギガビット 100MHz 工事担任者,IEEE802.3btとして標準化されたPoEのType4|IEEE802.3btとして標準化されたPoEのType4 規格 工事担任者,IEEE802.3btType4|IEEE802.3btType4 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>誘導雷サージ|雷害 誘導雷サージ 工事担任者</t>
+          <t>サージ防護|サージ防護 SPD 雷 過電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25319,7 +25319,7 @@
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,4B/5B符号化|4B/5B符号化 FDDI 100BASE-TX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>TDMA (時分割多元接続)|TDMA (時分割多元接続) GE-PON 衝突回避 タイムスロット 工事担任者,FDMA|FDMA 周波数分割多元接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>TELNET/SSH|TELNET/SSH 工事担任者</t>
+          <t>VLAN (仮想LAN)|VLAN (仮想LAN) IEEE802.1Q タグ セグメント 工事担任者,SSH|SSH 暗号化リモートログイン 公開鍵認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25603,7 +25603,7 @@
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者,IPv4|IPv4 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25703,7 +25703,7 @@
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>MPLS網の構成など|MPLS網の構成など 工事担任者,EoMPLS|EoMPLS MPLS 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25796,7 +25796,7 @@
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>SMTP AUTH|SMTP AUTH 工事担任者</t>
+          <t>SPFレコード|SPFレコード 送信ドメイン認証 メール なりすまし防止 工事担任者,DKIM|DKIM 電子署名 メール認証 送信ドメイン 公開鍵 工事担任者,デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25896,7 +25896,7 @@
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>電子データの送受信における脅威とその対策|電子データの送受信における脅威とその対策 工事担任者</t>
+          <t>PKI (公開鍵基盤)|PKI (公開鍵基盤) 電子証明書 CA 認証局 デジタル署名 工事担任者,デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25996,7 +25996,7 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>コンピュータウイルス対策|コンピュータウイルス対策 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>サニタイジング|サニタイジング 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26180,7 @@
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>非形式的アプローチ|非形式的アプローチ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26373,7 +26373,7 @@
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atとして標準化されたPoEのType1では|IEEE802.3atとして標準化されたPoEのType1では 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>IPv4|IPv4 工事担任者</t>
+          <t>IPv4|IPv4 パケット フラグメント TTL DFビット 中継ノード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>CSMA/CD|CSMA/CD イーサネット 工事担任者,ツイストペアケーブル|ツイストペアケーブル 工事担任者</t>
+          <t>全二重/半二重通信|全二重/半二重通信 イーサネット 衝突 再送処理 CSMA/CD 工事担任者,CSMA/CD|CSMA/CD 衝突検出 イーサネット 半二重 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26843,7 +26843,7 @@
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26936,7 +26936,7 @@
       </c>
       <c r="W274" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>職場における安全活動など|職場における安全活動など 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27143,7 +27143,7 @@
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム 工程管理 工事担任者,クリティカルパス|クリティカルパス 工程管理 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27332,7 +27332,7 @@
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>電気通信事業法施行規則に規定する緊急に行うことを要する通信|電気通信事業法施行規則に規定する緊急に行うことを要する通信 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27802,7 +27802,7 @@
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣|工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者,資格者証の書換え交付|資格者証の書換え交付 住所変更 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28012,7 +28012,7 @@
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>有線電気通信法に規定する｢目的｣、｢定義｣、｢設備の検査等｣又は｢技術基準｣|有線電気通信法に規定する｢目的｣、｢定義｣、｢設備の検査等｣又は｢技術基準｣ 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="W286" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>鳴音|鳴音防止条件 技術基準 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>｢絶縁抵抗等｣|｢絶縁抵抗等｣ 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28508,7 +28508,7 @@
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>配線設備等の評価雑音電力|評価雑音電力 配線設備 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,端末設備の安全性|端末設備の安全性 評価雑音電力 安全 法規 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>｢端末設備内において電波を使用する端末設備｣|｢端末設備内において電波を使用する端末設備｣ 工事担任者</t>
+          <t>端末設備内電波使用 空き状態確認|端末設備内電波使用 空き状態確認 周波数 通信路設定 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28708,7 +28708,7 @@
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28807,7 +28807,7 @@
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>移動電話端末の｢漏話減衰量｣及び｢発信の機能｣|移動電話端末の｢漏話減衰量｣及び｢発信の機能｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28899,7 +28899,7 @@
       </c>
       <c r="W294" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="W296" t="inlineStr">
         <is>
-          <t>電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29196,7 +29196,7 @@
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29295,7 +29295,7 @@
       </c>
       <c r="W298" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29387,7 @@
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29479,7 +29479,7 @@
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29571,7 +29571,7 @@
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29676,7 +29676,7 @@
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>GE-PONシステム|GE-PONシステム 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29769,7 +29769,7 @@
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SIP|SIPプロトコル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>Wi-Fi|Wi-Fi 無線LAN 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,OFDMA|OFDMA LTE 5G 周波数分割 工事担任者,TDMA (時分割多元接続)|TDMA (時分割多元接続) GE-PON 衝突回避 タイムスロット 工事担任者,CDMA|CDMA 移動通信 スペクトラム拡散 工事担任者,FDMA|FDMA 周波数分割多元接続 工事担任者,IEEE802.11axとして標準化され|IEEE802.11axとして標準化され 規格 工事担任者,IEEE802.11ax|IEEE802.11ax 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atとして標準化されたPoEのType1|IEEE802.3atとして標準化されたPoEのType1 規格 工事担任者,IEEE802.3atType1|IEEE802.3atType1 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30048,7 +30048,7 @@
       </c>
       <c r="W306" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>サージ防護|サージ防護 SPD 雷 過電圧 工事担任者,JIS A 4201|JIS A 4201 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30141,7 +30141,7 @@
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>10GBASE|10GBASE 工事担任者</t>
+          <t>10GBASE-LR|10GBASE-LR 物理層 64B/66B符号化 シングルモード 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,4B/5B符号化|4B/5B符号化 FDDI 100BASE-TX 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者,スクランブル処理|スクランブル処理 ブロック化 符号化 MAC副層 64B/66B 工事担任者,MAC副層|MAC副層 データリンク層 送信データ ブロック化 工事担任者,同期ヘッダ付加|同期ヘッダ付加 64B/66B 2ビット 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,VDSL|VDSL 工事担任者,光ファイバ|光ファイバ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,VDSL|VDSL 超高速DSL 短距離 マンション 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30324,7 +30324,7 @@
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>ファイアウォール|ファイアウォール 工事担任者</t>
+          <t>ファイアウォール|ファイアウォール パケットフィルタリング ステートフル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="W310" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者,IPv4|IPv4 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>MACアドレスなど|MACアドレスなど 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30600,7 +30600,7 @@
       </c>
       <c r="W312" t="inlineStr">
         <is>
-          <t>バッファオーバフロー|バッファオーバフロー攻撃 工事担任者</t>
+          <t>バッファオーバーフロー攻撃|バッファオーバーフロー攻撃 スタック 不正書換 任意プログラム実行 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30693,7 +30693,7 @@
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>しきい値|しきい値 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30793,7 +30793,7 @@
       </c>
       <c r="W314" t="inlineStr">
         <is>
-          <t>UNIX(セキュアOSを除く)のアクセス管理など|UNIX(セキュアOSを除く)のアクセス管理など 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30886,7 @@
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>職務分離の原則|職務分離の原則 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30992,7 +30992,7 @@
       </c>
       <c r="W316" t="inlineStr">
         <is>
-          <t>ISMS|ISMS 情報セキュリティマネジメント 工事担任者</t>
+          <t>ISMS (情報セキュリティマネジメント)|ISMS (情報セキュリティマネジメント) JIS Q 27001 リスク管理 工事担任者,JIS Q 2700|JIS Q 2700 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31082,7 +31082,7 @@
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="W318" t="inlineStr">
         <is>
-          <t>JIS C 0303 構内電気設備の配線用図記号|JIS C 0303 配線用図記号 工事担任者</t>
+          <t>JIS C 0303|JIS C 0303 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31344,7 +31344,7 @@
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31442,7 +31442,7 @@
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="W322" t="inlineStr">
         <is>
-          <t>T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31633,7 @@
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="W324" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31819,7 +31819,7 @@
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>予測平均温冷感申告|予測平均温冷感申告 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31925,7 +31925,7 @@
       </c>
       <c r="W326" t="inlineStr">
         <is>
-          <t>図2に示すアローダイアグラム|図2に示すアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32120,7 +32120,7 @@
       </c>
       <c r="W328" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢工事担任者資格者証｣|電気通信事業法に規定する｢工事担任者資格者証｣ 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32214,7 +32214,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32306,7 +32306,7 @@
       </c>
       <c r="W330" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32398,7 +32398,7 @@
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>電気通信事業法施行規則|電気通信事業法施行規則 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32503,7 +32503,7 @@
       </c>
       <c r="W332" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32602,7 +32602,7 @@
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の返納｣及び｢資格者証の交付｣|工事担任者規則に規定する｢資格者証の返納｣及び｢資格者証の交付｣ 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32694,7 +32694,7 @@
       </c>
       <c r="W334" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則の登録認定機関による技術基準適合認定の｢表示｣|端末機器の技術基準適合認定等に関する規則の登録認定機関による技術基準適合認定の｢表示｣ 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>基礎的電気通信役務|基礎的電気通信役務 ユニバーサルサービス 提供義務 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32878,7 +32878,7 @@
       </c>
       <c r="W336" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33079,7 +33079,7 @@
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>｢鳴音の発生防止｣|｢鳴音の発生防止｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33172,7 +33172,7 @@
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>配線設備等の技術基準|配線設備等 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33272,7 +33272,7 @@
       </c>
       <c r="W340" t="inlineStr">
         <is>
-          <t>｢絶縁抵抗等｣及び｢配線設備等｣|｢絶縁抵抗等｣及び｢配線設備等｣ 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33365,7 +33365,7 @@
       </c>
       <c r="W341" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 アクセス制御 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33466,7 +33466,7 @@
       </c>
       <c r="W342" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33564,7 +33564,7 @@
       </c>
       <c r="W343" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="W344" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者,インピーダンス|インピーダンス 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33752,7 +33752,7 @@
       </c>
       <c r="W345" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>｢インターネットプロトコルを使用する専用通信回線設備等端末｣|｢インターネットプロトコルを使用する専用通信回線設備等端末｣ 工事担任者,アクセス制御|アクセス制御 工事担任者,識別符号|識別符号 アクセス制御 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33947,7 +33947,7 @@
       </c>
       <c r="W347" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する｢架空電線の高さ｣及び｢架空電線の支持物｣|有線電気通信設備令に規定する｢架空電線の高さ｣及び｢架空電線の支持物｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34138,7 +34138,7 @@
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>不正アクセス行為の禁止等に関する法律に規定する事項|不正アクセス行為の禁止等に関する法律に規定する事項 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34319,7 +34319,7 @@
       </c>
       <c r="W351" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34407,7 +34407,7 @@
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,光スプリッタ|光スプリッタ PON 光分岐 受動素子 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34500,7 +34500,7 @@
       </c>
       <c r="W353" t="inlineStr">
         <is>
-          <t>PBX|PBX 構内交換機 工事担任者</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ アナログ電話 IP変換 PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34606,7 +34606,7 @@
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>100BASE-TX|100BASE-TX ファストイーサネット UTP 工事担任者,PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atとして標準化されたPoEのType1又はType2について述|IEEE802.3atとして標準化されたPoEのType1又はType2について述 規格 工事担任者,IEEE802.3atには|IEEE802.3atには 規格 工事担任者,IEEE802.3afの規格がType1として含|IEEE802.3afの規格がType1として含 規格 工事担任者,IEEE802.3afがType1として含まれる|IEEE802.3afがType1として含まれる 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34699,7 +34699,7 @@
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>5G|5G 移動通信 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,IEEE802.11標準の無線LAN規格のうち|IEEE802.11標準の無線LAN規格のうち 規格 工事担任者,IEEE802.11n及びIEEE802|IEEE802.11n及びIEEE802 規格 工事担任者,IEEE802.11a及びIEEE802|IEEE802.11a及びIEEE802 規格 工事担任者,IEEE802.11ac及びIEEE802|IEEE802.11ac及びIEEE802 規格 工事担任者,IEEE802.11nおよびIEEE802|IEEE802.11nおよびIEEE802 規格 工事担任者,IEEE802.11aと802|IEEE802.11aと802 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>SPD|SPD サージ防護デバイス 工事担任者,インピーダンス|インピーダンス 工事担任者</t>
+          <t>SPD (サージ防護デバイス)|SPD (サージ防護デバイス) JIS C 5381 雷サージ 過電圧保護 工事担任者,サージ防護|サージ防護 SPD 雷 過電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34885,7 +34885,7 @@
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34978,7 +34978,7 @@
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>SS方式 (シングルスター)|SS方式 (シングルスター) 光アクセス 1対1 分岐なし 工事担任者,PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,メディアコンバータ|メディアコンバータ 光-電気変換 光アクセス SS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35071,7 +35071,7 @@
       </c>
       <c r="W359" t="inlineStr">
         <is>
-          <t>SaaS|SaaS 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35169,7 +35169,7 @@
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者</t>
+          <t>フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35262,7 +35262,7 @@
       </c>
       <c r="W361" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS MPLS 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>アドレススキャン|アドレススキャン 工事担任者</t>
+          <t>DoS/DDoS攻撃|DoS/DDoS攻撃 サービス妨害 帯域消費 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35448,7 +35448,7 @@
       </c>
       <c r="W363" t="inlineStr">
         <is>
-          <t>リスクベース認証|リスクベース認証 工事担任者</t>
+          <t>CHAP認証|CHAP認証 PPP チャレンジ応答 ハッシュ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35538,7 +35538,7 @@
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>ネットワーク利用時における情報漏洩対策|ネットワーク利用時における情報漏洩対策 工事担任者,TLS|TLS暗号化 工事担任者,SMTP|SMTPメールプロトコル 工事担任者</t>
+          <t>情報漏洩対策|情報漏洩対策 セキュリティ 暗号化 TLS スニッフィング 工事担任者,スニッフィング対策|スニッフィング対策 盗聴 暗号化 TLS セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="W365" t="inlineStr">
         <is>
-          <t>デジタル証明書|デジタル証明書 PKI 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35737,7 +35737,7 @@
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>ISMS|ISMS 情報セキュリティマネジメント 工事担任者,JIS Q 27001|JIS Q 27001 ISMS 工事担任者</t>
+          <t>ISMS (情報セキュリティマネジメント)|ISMS (情報セキュリティマネジメント) JIS Q 27001 リスク管理 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者,JIS Q 2700|JIS Q 2700 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35813,7 +35813,7 @@
       </c>
       <c r="W367" t="inlineStr">
         <is>
-          <t>JIS C 0303 構内電気設備の配線用図記号|JIS C 0303 配線用図記号 工事担任者</t>
+          <t>JIS C 0303|JIS C 0303 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35914,7 +35914,7 @@
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6841|JIS C 6841 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36007,7 +36007,7 @@
       </c>
       <c r="W369" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36113,7 +36113,7 @@
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>平衡ケーブルを用いたLAN配線のフィールドテストなど|平衡ケーブルを用いたLAN配線のフィールドテストなど 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="W371" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36304,7 +36304,7 @@
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>細径低摩擦|細径低摩擦 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36405,7 +36405,7 @@
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36498,7 +36498,7 @@
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>ツイストペアケーブル|ツイストペアケーブル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36588,7 +36588,7 @@
       </c>
       <c r="W375" t="inlineStr">
         <is>
-          <t>JIS Z 9020-2:2023管理図-第2部:シューハート管理図に基づく統計的工 程管理など|JIS Z 9020-2:2023管理図-第2部:シューハート管理図に基づく統計的工 程管理など 工事担任者</t>
+          <t>JIS Z 9020|JIS Z 9020 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36694,7 +36694,7 @@
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>工程管理などに用いられるアローダイアグラム|工程管理などに用いられるアローダイアグラム 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者,フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36799,7 +36799,7 @@
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36891,7 +36891,7 @@
       </c>
       <c r="W378" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36983,7 +36983,7 @@
       </c>
       <c r="W379" t="inlineStr">
         <is>
-          <t>電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37174,7 +37174,7 @@
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>電気通信事業法施行規則に規定する緊急に行うことを要する通信|電気通信事業法施行規則に規定する緊急に行うことを要する通信 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37358,7 +37358,7 @@
       </c>
       <c r="W383" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の交付｣及び｢資格者証の再交付｣|工事担任者規則に規定する｢資格者証の交付｣及び｢資格者証の再交付｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者,資格者証の書換え交付|資格者証の書換え交付 住所変更 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37447,7 +37447,7 @@
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則の登録認定機関による技術基準適合認定の｢表示｣|端末機器の技術基準適合認定等に関する規則の登録認定機関による技術基準適合認定の｢表示｣ 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37539,7 +37539,7 @@
       </c>
       <c r="W385" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者,管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37631,7 +37631,7 @@
       </c>
       <c r="W386" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="W387" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>自動的に記録する容量|自動的に記録する容量 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37925,7 +37925,7 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>端末設備機器の接地抵抗|接地抵抗 端末設備 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38024,7 +38024,7 @@
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>｢配線設備等｣|｢配線設備等｣ 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,端末設備の安全性|端末設備の安全性 評価雑音電力 安全 法規 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38116,7 +38116,7 @@
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>電波の周波数|電波の周波数 工事担任者</t>
+          <t>端末設備内電波使用 空き状態確認|端末設備内電波使用 空き状態確認 周波数 通信路設定 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38221,7 +38221,7 @@
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号|アナログ電話端末の｢選択信号の条件｣における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38316,7 +38316,7 @@
       </c>
       <c r="W393" t="inlineStr">
         <is>
-          <t>移動電話端末の｢基本的機能｣又は｢発信の機能｣|移動電話端末の｢基本的機能｣又は｢発信の機能｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>インターネットプロトコル電話端末の｢電気的条件等｣及び｢緊急通報機能｣|インターネットプロトコル電話端末の｢電気的条件等｣及び｢緊急通報機能｣ 工事担任者</t>
+          <t>分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38499,7 +38499,7 @@
       </c>
       <c r="W395" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="W396" t="inlineStr">
         <is>
-          <t>漏話|漏話 クロストーク 工事担任者,専用通信回線|専用通信回線設備等端末 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38701,7 +38701,7 @@
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38793,7 +38793,7 @@
       </c>
       <c r="W398" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38887,7 +38887,7 @@
       </c>
       <c r="W399" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38986,7 +38986,7 @@
       </c>
       <c r="W400" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,識別符号|識別符号 アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39078,7 +39078,7 @@
       </c>
       <c r="W401" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="W402" t="inlineStr">
         <is>
-          <t>WDM|WDM 光波長多重 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者,TDMA|TDMA 時分割多重 工事担任者</t>
+          <t>10G-EPON|10G-EPON 次世代PON 工事担任者,IEEE802.3avとして標準化された10G|IEEE802.3avとして標準化された10G 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39261,7 +39261,7 @@
       </c>
       <c r="W403" t="inlineStr">
         <is>
-          <t>SIP|SIPプロトコル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       </c>
       <c r="W404" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者,PoE|PoE 給電 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atとして標準化されたPoEの規格において|IEEE802.3atとして標準化されたPoEの規格において 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39442,7 +39442,7 @@
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>IEEE802.11ax 無線LAN周波数帯|IEEE802.11ax Wi-Fi6 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,Wi-Fi|Wi-Fi 無線LAN IEEE802.11 工事担任者,IEEE802.11axとして標準化された無線LAN規格において|IEEE802.11axとして標準化された無線LAN規格において 規格 工事担任者,IEEE802.11ax|IEEE802.11ax 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39542,7 +39542,7 @@
       </c>
       <c r="W406" t="inlineStr">
         <is>
-          <t>商用電源を使用するネットワーク機器のノイズ対策に用いられるデバイス|商用電源を使用するネットワーク機器のノイズ対策に用いられるデバイス 工事担任者,インピーダンス|インピーダンス 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39635,7 +39635,7 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者,MAC副層|MAC副層 データリンク層 送信データ ブロック化 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39728,7 +39728,7 @@
       </c>
       <c r="W408" t="inlineStr">
         <is>
-          <t>CATV|CATVシステム 工事担任者,光ファイバ|光ファイバ 工事担任者,変調|変調方式 工事担任者</t>
+          <t>OFDM|OFDM 直交周波数分割多重 マルチキャリア 工事担任者,CATVシステム|CATVシステム ヘッドエンド HFC 同軸 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者,FDMA|FDMA 周波数分割多元接続 工事担任者,CSMA/CD|CSMA/CD 衝突検出 イーサネット 半二重 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39821,7 +39821,7 @@
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>IPv6|IPv6 工事担任者,ICMP|ICMPプロトコル 工事担任者</t>
+          <t>IPv6拡張ヘッダ|IPv6拡張ヘッダ 断片化 ルーティング 中継ノード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39914,7 +39914,7 @@
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>VoIP|VoIP 音声IP 工事担任者</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ アナログ電話 IP変換 PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="W411" t="inlineStr">
         <is>
-          <t>広域イーサネット及びMPLS網|広域イーサネット及びMPLS網 工事担任者</t>
+          <t>広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40097,7 +40097,7 @@
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>サンドボックス|サンドボックス 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
       </c>
       <c r="W413" t="inlineStr">
         <is>
-          <t>暗号方式の特徴など|暗号方式の特徴など 工事担任者</t>
+          <t>PKI (公開鍵基盤)|PKI (公開鍵基盤) 電子証明書 CA 認証局 デジタル署名 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40293,7 +40293,7 @@
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>クロスサイトスクリプティング|クロスサイトスクリプティング 工事担任者</t>
+          <t>SQLインジェクション|SQLインジェクション データベース攻撃 Webセキュリティ 工事担任者,クロスサイトスクリプティング (XSS)|クロスサイトスクリプティング (XSS) Webセキュリティ スクリプト注入 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40393,7 +40393,7 @@
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>IPsec及びIPsec-VPN|IPsec及びIPsec-VPN 工事担任者</t>
+          <t>IPsec|IPsec VPN 暗号化 トンネル AH ESP IKE 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40486,7 +40486,7 @@
       </c>
       <c r="W416" t="inlineStr">
         <is>
-          <t>CSIRT|CSIRT 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40592,7 +40592,7 @@
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6841|JIS C 6841 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40685,7 +40685,7 @@
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40775,7 +40775,7 @@
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法|JIS C 6823:2010光ファイバ損失試験方法におけるOTDR法 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40868,7 +40868,7 @@
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40966,7 +40966,7 @@
       </c>
       <c r="W421" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者,JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41059,7 +41059,7 @@
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>40GBASE-T LANケーブル|40GBASE-T カテゴリ8 工事担任者</t>
+          <t>IEEE802.3bqとして標準化された40GBASE|IEEE802.3bqとして標準化された40GBASE 規格 工事担任者,IEEE802.3bq|IEEE802.3bq 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41152,7 +41152,7 @@
       </c>
       <c r="W423" t="inlineStr">
         <is>
-          <t>OTDR|OTDR 光ファイバ損失 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>後方散乱光 (OTDR測定)|後方散乱光 (OTDR測定) OTDR 光ファイバ 損失 障害 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者,JIS X 5151|JIS X 5151 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41245,7 +41245,7 @@
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41346,7 +41346,7 @@
       </c>
       <c r="W425" t="inlineStr">
         <is>
-          <t>JIS Q 9024|JIS Q 9024 継続的改善 工事担任者</t>
+          <t>JIS Q 9024|JIS Q 9024 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41439,7 +41439,7 @@
       </c>
       <c r="W426" t="inlineStr">
         <is>
-          <t>仮説立案|仮説立案 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41539,7 +41539,7 @@
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢工事担任者資格者証｣|電気通信事業法に規定する｢工事担任者資格者証｣ 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41638,7 +41638,7 @@
       </c>
       <c r="W428" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41737,7 +41737,7 @@
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する｢管理規程｣及び｢基礎的電気通信役務の提供｣|電気通信事業法に規定する｢管理規程｣及び｢基礎的電気通信役務の提供｣ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者,基礎的電気通信役務|基礎的電気通信役務 ユニバーサルサービス 提供義務 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41829,7 +41829,7 @@
       </c>
       <c r="W430" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者,登録認定機関|登録認定機関 工事担任者,技術基準適合認定|技術基準適合認定 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41921,7 +41921,7 @@
       </c>
       <c r="W431" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42026,7 +42026,7 @@
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42125,7 +42125,7 @@
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣|工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42214,7 +42214,7 @@
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>端末機器の技術基準適合認定等に関する規則|端末機器の技術基準適合認定等に関する規則 工事担任者,専用通信回線|専用通信回線設備等端末 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42319,7 +42319,7 @@
       </c>
       <c r="W435" t="inlineStr">
         <is>
-          <t>有線電気通信法に規定する｢目的｣、｢定義｣、｢設備の検査等｣又は｢技術基準｣|有線電気通信法に規定する｢目的｣、｢定義｣、｢設備の検査等｣又は｢技術基準｣ 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42406,7 +42406,7 @@
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="W437" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42610,7 +42610,7 @@
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>｢責任の分界｣及び安全性等|｢責任の分界｣及び安全性等 工事担任者,鳴音|鳴音防止条件 技術基準 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42702,7 +42702,7 @@
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者,配線設備等の絶縁抵抗|配線設備等の絶縁抵抗 直流200V 1MΩ 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42886,7 +42886,7 @@
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>識別符号|識別符号 アクセス制御 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42978,7 +42978,7 @@
       </c>
       <c r="W442" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>直流回路|直流回路 アナログ電話 交換設備 2線式 開始終了制御 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="W443" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者,総合デジタル通信端末|総合デジタル通信端末 ISDN 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43182,7 +43182,7 @@
       </c>
       <c r="W444" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末の｢電気的条件等｣|専用通信回線設備等端末の｢電気的条件等｣ 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="W445" t="inlineStr">
         <is>
-          <t>｢インターネットプロトコルを使用する専用通信回線設備等端末｣|｢インターネットプロトコルを使用する専用通信回線設備等端末｣ 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43381,7 +43381,7 @@
       </c>
       <c r="W446" t="inlineStr">
         <is>
-          <t>アナログ電話端末等の選択信号における押しボタンダイヤル信号|アナログ電話端末等の選択信号における押しボタンダイヤル信号 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43470,7 +43470,7 @@
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する｢屋内電線｣及び｢有線電気通信設備の保安｣|有線電気通信設備令に規定する｢屋内電線｣及び｢有線電気通信設備の保安｣ 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43575,7 +43575,7 @@
       </c>
       <c r="W448" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43667,7 +43667,7 @@
       </c>
       <c r="W449" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43759,7 +43759,7 @@
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43851,7 +43851,7 @@
       </c>
       <c r="W451" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43944,7 +43944,7 @@
       </c>
       <c r="W452" t="inlineStr">
         <is>
-          <t>G-PON|G-PON 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,XG-PON|XG-PON 次世代PON 光アクセス 工事担任者,IEEE802.3av規格|IEEE802.3av規格 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44044,7 +44044,7 @@
       </c>
       <c r="W453" t="inlineStr">
         <is>
-          <t>IP-PBX|IP-PBX 工事担任者,SIP|SIPプロトコル 工事担任者,TCP|TCPプロトコル 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="W454" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者,ツイストペアケーブル|ツイストペアケーブル 工事担任者</t>
+          <t>PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,PoE++ (IEEE802.3bt)|PoE++ (IEEE802.3bt) 高電力給電 4ペア 90W 工事担任者,カテゴリ5e UTP|カテゴリ5e UTP ギガビット 100MHz 工事担任者,IEEE802.3btとして標準化されたPoEのType4|IEEE802.3btとして標準化されたPoEのType4 規格 工事担任者,IEEE802.3btType4|IEEE802.3btType4 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44230,7 +44230,7 @@
       </c>
       <c r="W455" t="inlineStr">
         <is>
-          <t>プローブ応答|プローブ応答 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,無線LANアクセスポイント|無線LANアクセスポイント Wi-Fi SSID BSS 工事担任者,IEEE802.11nとして標準化された無線LAN規格では|IEEE802.11nとして標準化された無線LAN規格では 規格 工事担任者,IEEE802.11nで複数のデータフレームへの確認応答を1回にまとめて送信するのはブロックACKフレーム|IEEE802.11nで複数のデータフレームへの確認応答を1回にまとめて送信するのはブロックACKフレーム 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="W456" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>サージ防護|サージ防護 SPD 雷 過電圧 工事担任者,JIS A 4201|JIS A 4201 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44416,7 +44416,7 @@
       </c>
       <c r="W457" t="inlineStr">
         <is>
-          <t>10GBASE|10GBASE 工事担任者</t>
+          <t>10GBASE-LR|10GBASE-LR 物理層 64B/66B符号化 シングルモード 工事担任者,64B/66B符号化方式|64B/66B符号化方式 スクランブル 同期ヘッダ 10GBASE MAC副層 工事担任者,8B/10B符号化|8B/10B符号化 ギガビットイーサネット DC平衡 工事担任者,4B/5B符号化|4B/5B符号化 FDDI 100BASE-TX 工事担任者,8B/6T符号化|8B/6T符号化 100BASE-T4 3値符号 工事担任者,スクランブル処理|スクランブル処理 ブロック化 符号化 MAC副層 64B/66B 工事担任者,MAC副層|MAC副層 データリンク層 送信データ ブロック化 工事担任者,同期ヘッダ付加|同期ヘッダ付加 64B/66B 2ビット 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>CATV|CATVシステム 工事担任者,光ファイバ|光ファイバ 工事担任者,同軸ケーブル|同軸ケーブル 工事担任者</t>
+          <t>FTTH|FTTH 光ファイバ 宅内 アクセス 工事担任者,ADSL|ADSL 非対称DSL 電話線 ブロードバンド 工事担任者,VDSL|VDSL 超高速DSL 短距離 マンション 工事担任者,CATVシステム|CATVシステム ヘッドエンド HFC 同軸 工事担任者,CATVヘッドエンド|CATVヘッドエンド 映像配信 信号変換 工事担任者,HFC (光同軸混合網)|HFC (光同軸混合網) CATV 光ファイバ 同軸ケーブル 工事担任者,CATVの光ノード|CATVの光ノード HFC 光-同軸変換 工事担任者,同軸ケーブル|同軸ケーブル CATV HFC インピーダンス 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44602,7 +44602,7 @@
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>DaaS|DaaS 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44703,7 +44703,7 @@
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>IPv6アドレス|IPv6アドレス 工事担任者</t>
+          <t>フロート (TF/FF)|フロート (TF/FF) アローダイアグラム 余裕時間 クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44793,7 +44793,7 @@
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>MACフレームなど|MACフレームなど 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44886,7 +44886,7 @@
       </c>
       <c r="W462" t="inlineStr">
         <is>
-          <t>クラスタリング|クラスタリング 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="W463" t="inlineStr">
         <is>
-          <t>SMTP AUTH|SMTP AUTH 工事担任者</t>
+          <t>送信ドメイン認証技術|送信ドメイン認証技術 SPF DKIM DMARC メール なりすまし対策 工事担任者,SPFレコード|SPFレコード 送信ドメイン認証 メール なりすまし防止 工事担任者,DKIM|DKIM 電子署名 メール認証 送信ドメイン 公開鍵 工事担任者,デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45072,7 +45072,7 @@
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>HTTP|HTTP 工事担任者</t>
+          <t>スニッフィング対策|スニッフィング対策 盗聴 暗号化 TLS セキュリティ 工事担任者,DHCP|DHCP IPアドレス自動割り当て リース 工事担任者,SSH|SSH 暗号化リモートログイン 公開鍵認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45172,7 +45172,7 @@
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>サイバー攻撃の種類|サイバー攻撃の種類 工事担任者</t>
+          <t>スニッフィング対策|スニッフィング対策 盗聴 暗号化 TLS セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45278,7 +45278,7 @@
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>ISMS|ISMS 情報セキュリティマネジメント 工事担任者,JIS Q 27001|JIS Q 27001 ISMS 工事担任者</t>
+          <t>ISMS (情報セキュリティマネジメント)|ISMS (情報セキュリティマネジメント) JIS Q 27001 リスク管理 工事担任者,JIS Q 2700|JIS Q 2700 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45371,7 +45371,7 @@
       </c>
       <c r="W467" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45447,7 +45447,7 @@
       </c>
       <c r="W468" t="inlineStr">
         <is>
-          <t>JIS C 0303 構内電気設備の配線用図記号|JIS C 0303 配線用図記号 工事担任者</t>
+          <t>JIS C 0303|JIS C 0303 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45540,7 +45540,7 @@
       </c>
       <c r="W469" t="inlineStr">
         <is>
-          <t>UTP|UTPケーブル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45630,7 +45630,7 @@
       </c>
       <c r="W470" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45824,7 +45824,7 @@
       </c>
       <c r="W472" t="inlineStr">
         <is>
-          <t>UTP|UTPケーブル 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45917,7 +45917,7 @@
       </c>
       <c r="W473" t="inlineStr">
         <is>
-          <t>光コネクタ|光コネクタ 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46010,7 +46010,7 @@
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>ICMP|ICMP 工事担任者</t>
+          <t>ICMP/ICMPv6|ICMP/ICMPv6 制御メッセージ エラー通知 到達不能 工事担任者,SNMP|SNMP ネットワーク管理 MIB トラップ 工事担任者,IEEE802.1Dにより|IEEE802.1Dにより 規格 工事担任者,IEEE802.1Dで標準化されたプロトコルはSTP|IEEE802.1Dで標準化されたプロトコルはSTP 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="W475" t="inlineStr">
         <is>
-          <t>施工出来高と工事総原価|施工管理 原価管理 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46219,7 +46219,7 @@
       </c>
       <c r="W476" t="inlineStr">
         <is>
-          <t>アローダイアグラム|アローダイアグラム 工程管理 工事担任者,クリティカルパス|クリティカルパス 工程管理 工事担任者</t>
+          <t>アローダイアグラム クリティカルパス|アローダイアグラム クリティカルパス PERT 工程管理 最長経路 TF 工事担任者,クリティカルパス|クリティカルパス アローダイアグラム PERT 最長工期 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46324,7 +46324,7 @@
       </c>
       <c r="W477" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46416,7 +46416,7 @@
       </c>
       <c r="W478" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46513,7 +46513,7 @@
       </c>
       <c r="W479" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>管理規程 (電気通信事業)|管理規程 (電気通信事業) 電気通信事業法 総務大臣 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46612,7 +46612,7 @@
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46707,7 +46707,7 @@
       </c>
       <c r="W481" t="inlineStr">
         <is>
-          <t>電気通信事業法施行規則に規定する緊急に行うことを要する通信|電気通信事業法施行規則に規定する緊急に行うことを要する通信 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46797,7 +46797,7 @@
       </c>
       <c r="W482" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣|工事担任者規則に規定する｢資格者証の種類及び工事の範囲｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46896,7 +46896,7 @@
       </c>
       <c r="W483" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣|工事担任者規則に規定する｢資格者証の再交付｣及び｢資格者証の返納｣ 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者,資格者証の書換え交付|資格者証の書換え交付 住所変更 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46990,7 +46990,7 @@
       </c>
       <c r="W484" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47082,7 +47082,7 @@
       </c>
       <c r="W485" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47174,7 +47174,7 @@
       </c>
       <c r="W486" t="inlineStr">
         <is>
-          <t>非常事態における有線電気通信設備の運用|有線電気通信法 非常事態 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47274,7 +47274,7 @@
       </c>
       <c r="W487" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47373,7 +47373,7 @@
       </c>
       <c r="W488" t="inlineStr">
         <is>
-          <t>｢責任の分界｣及び安全性等|｢責任の分界｣及び安全性等 工事担任者</t>
+          <t>責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47470,7 +47470,7 @@
       </c>
       <c r="W489" t="inlineStr">
         <is>
-          <t>絶縁抵抗|絶縁抵抗 電気通信端末 工事担任者</t>
+          <t>絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47559,7 +47559,7 @@
       </c>
       <c r="W490" t="inlineStr">
         <is>
-          <t>｢配線設備等｣|｢配線設備等｣ 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47651,7 +47651,7 @@
       </c>
       <c r="W491" t="inlineStr">
         <is>
-          <t>金属製の|金属製の 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47743,7 +47743,7 @@
       </c>
       <c r="W492" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者,総合デジタル通信端末|総合デジタル通信端末 ISDN 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47843,7 +47843,7 @@
       </c>
       <c r="W493" t="inlineStr">
         <is>
-          <t>固定電話端末の｢識別情報登録｣|固定電話端末の｢識別情報登録｣ 工事担任者,用語|電気通信用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47932,7 +47932,7 @@
       </c>
       <c r="W494" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48024,7 +48024,7 @@
       </c>
       <c r="W495" t="inlineStr">
         <is>
-          <t>電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48124,7 +48124,7 @@
       </c>
       <c r="W496" t="inlineStr">
         <is>
-          <t>アナログ電話端末等の選択信号における押しボタンダイヤル信号の条件|アナログ電話端末等の選択信号における押しボタンダイヤル信号の条件 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48224,7 +48224,7 @@
       </c>
       <c r="W497" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する用語|有線電気通信設備令に規定する用語 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48313,7 +48313,7 @@
       </c>
       <c r="W498" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48405,7 +48405,7 @@
       </c>
       <c r="W499" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48497,7 +48497,7 @@
       </c>
       <c r="W500" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48591,7 +48591,7 @@
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>電子署名及び認証業務に関する法律に規定する事項|電子署名及び認証業務に関する法律に規定する事項 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48682,7 +48682,7 @@
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>GE-PON|GE-PON 工事担任者,WDM|WDM 光波長多重 工事担任者,OLT|OLT PON 工事担任者,ONU|ONU PON 工事担任者,TDMA|TDMA 時分割多重 工事担任者</t>
+          <t>GE-PON|GE-PON OLT ONU TDMA 光アクセス 工事担任者,10G-EPON|10G-EPON 次世代PON 工事担任者,IEEE802.3avとして標準化された10G|IEEE802.3avとして標準化された10G 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48773,7 +48773,7 @@
       </c>
       <c r="W503" t="inlineStr">
         <is>
-          <t>IP-PBX|IP-PBX 工事担任者</t>
+          <t>IP-PBX|IP-PBX VoIP 企業電話 SIP LAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48864,7 +48864,7 @@
       </c>
       <c r="W504" t="inlineStr">
         <is>
-          <t>PoE|PoE 給電 工事担任者</t>
+          <t>PoE+ (IEEE802.3at Type2)|PoE+ (IEEE802.3at Type2) PSE PD 600mA 50-57V 工事担任者,PoE (IEEE802.3af)|PoE (IEEE802.3af) PSE PD 350mA 電力供給 工事担任者,IEEE802.3atとして標準化されたPoEのType2|IEEE802.3atとして標準化されたPoEのType2 規格 工事担任者,IEEE802.3atType2|IEEE802.3atType2 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48955,7 +48955,7 @@
       </c>
       <c r="W505" t="inlineStr">
         <is>
-          <t>IEEE802.11標準の無線LAN|IEEE802.11標準の無線LAN 工事担任者</t>
+          <t>IEEE802.11無線LAN|IEEE802.11無線LAN Wi-Fi OFDM CSMA/CA 工事担任者,無線LANアクセスポイント|無線LANアクセスポイント Wi-Fi SSID BSS 工事担任者,IEEE802.11標準の無線LANについて述べた次の二つの記述は|IEEE802.11標準の無線LANについて述べた次の二つの記述は 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="W506" t="inlineStr">
         <is>
-          <t>EMC|EMC 電磁両立性 工事担任者,用語|電気通信用語 工事担任者</t>
+          <t>JIS C 6005|JIS C 6005 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49137,7 +49137,7 @@
       </c>
       <c r="W507" t="inlineStr">
         <is>
-          <t>1000BASE|1000BASE 工事担任者</t>
+          <t>1000BASE-T|1000BASE-T ギガビット イーサネット UTP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49228,7 +49228,7 @@
       </c>
       <c r="W508" t="inlineStr">
         <is>
-          <t>光アクセスネットワーク|光アクセスネットワーク 工事担任者,VDSL|VDSL 工事担任者,光ファイバ|光ファイバ 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>PDS方式 (光受動素子で分岐)|PDS方式 (光受動素子で分岐) PON スプリッタ 光分岐 工事担任者,光アクセスネットワーク設備構成|光アクセスネットワーク設備構成 OLT ONU PON SS PDS 工事担任者,光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49319,7 +49319,7 @@
       </c>
       <c r="W509" t="inlineStr">
         <is>
-          <t>SDH/SONET|SDH/SONET 工事担任者</t>
+          <t>VLAN (仮想LAN)|VLAN (仮想LAN) IEEE802.1Q タグ セグメント 工事担任者,SSH|SSH 暗号化リモートログイン 公開鍵認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49410,7 +49410,7 @@
       </c>
       <c r="W510" t="inlineStr">
         <is>
-          <t>IETFのRFC4443として標準化されたICMPv6など|IETFのRFC4443として標準化されたICMPv6など 工事担任者,IPv6|IPv6 工事担任者</t>
+          <t>MTU (最大転送単位)|MTU (最大転送単位) パケット分割 フラグメント 1500バイト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49501,7 +49501,7 @@
       </c>
       <c r="W511" t="inlineStr">
         <is>
-          <t>EoMPLS|EoMPLS MPLS 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
+          <t>EoMPLS|EoMPLS MPLS イーサネット 広域 ラベル 工事担任者,広域イーサネット|広域イーサネット MPLS VPN L2 WAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49592,7 +49592,7 @@
       </c>
       <c r="W512" t="inlineStr">
         <is>
-          <t>TCP|TCPプロトコル 工事担任者,DoS|DoS攻撃 工事担任者</t>
+          <t>DoS/DDoS攻撃|DoS/DDoS攻撃 サービス妨害 帯域消費 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49678,7 +49678,7 @@
       </c>
       <c r="W513" t="inlineStr">
         <is>
-          <t>バイオメトリクス認証|バイオメトリクス認証 利用者認証 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49769,7 +49769,7 @@
       </c>
       <c r="W514" t="inlineStr">
         <is>
-          <t>安全性|安全性 技術基準 工事担任者</t>
+          <t>端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49860,7 +49860,7 @@
       </c>
       <c r="W515" t="inlineStr">
         <is>
-          <t>syslog|syslog 工事担任者</t>
+          <t>SNMP|SNMP ネットワーク管理 MIB トラップ 工事担任者,syslog (UNIXシステムログ)|syslog (UNIXシステムログ) セキュリティ 監査ログ リモートホスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -49954,7 +49954,7 @@
       </c>
       <c r="W516" t="inlineStr">
         <is>
-          <t>情報セキュリティポリシー|情報セキュリティポリシー 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50045,7 +50045,7 @@
       </c>
       <c r="W517" t="inlineStr">
         <is>
-          <t>JIS C 6823|JIS C 6823 光ファイバ損失試験 工事担任者,光ファイバ|光ファイバ 工事担任者</t>
+          <t>JIS C 6823 光ファイバ試験|JIS C 6823 光ファイバ試験 OTDR 損失測定 工事担任者,JIS C 6823|JIS C 6823 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50136,7 +50136,7 @@
       </c>
       <c r="W518" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50227,7 +50227,7 @@
       </c>
       <c r="W519" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>通信技術|通信技術 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50321,7 +50321,7 @@
       </c>
       <c r="W520" t="inlineStr">
         <is>
-          <t>T568B|T568B 配線規格 工事担任者</t>
+          <t>T568B配線規格|T568B配線規格 RJ-45 UTP ピン番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50418,7 +50418,7 @@
       </c>
       <c r="W521" t="inlineStr">
         <is>
-          <t>平衡ケーブルを用いたLAN配線のフィールドテストなど|平衡ケーブルを用いたLAN配線のフィールドテストなど 工事担任者</t>
+          <t>光コネクタ挿入損失|光コネクタ挿入損失 JIS 測定 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="W522" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者</t>
+          <t>光ファイバケーブル|光ファイバケーブル SMF MMF 接続工事 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50600,7 +50600,7 @@
       </c>
       <c r="W523" t="inlineStr">
         <is>
-          <t>OITDA|OITDA プラスチック光ファイバ 工事担任者,光ファイバ|光ファイバ 工事担任者,プラスチック光ファイバ|プラスチック光ファイバ POF 工事担任者,伝送損失|伝送損失 工事担任者</t>
+          <t>光伝送損失|光伝送損失 パワーバジェット dB/km 工事担任者,プラスチック光ファイバ (POF)|プラスチック光ファイバ (POF) アクリル樹脂 短距離 OITDA 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50694,7 +50694,7 @@
       </c>
       <c r="W524" t="inlineStr">
         <is>
-          <t>JIS X 5150|JIS X 5150 構内情報通信網配線 工事担任者</t>
+          <t>JIS X 5150|JIS X 5150 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50785,7 +50785,7 @@
       </c>
       <c r="W525" t="inlineStr">
         <is>
-          <t>JIS Z 8141:2022生産管理用語の作業の維持・管理において、5Sの定義に記載されている用語|JIS Z 8141:2022生産管理用語の作業の維持・管理において、5Sの定義に記載されている用語 工事担任者</t>
+          <t>JIS Z 8141|JIS Z 8141 規格 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50876,7 +50876,7 @@
       </c>
       <c r="W526" t="inlineStr">
         <is>
-          <t>建設工事における施工計画及び施工管理|建設工事における施工計画及び施工管理 工事担任者</t>
+          <t>施工計画書|施工計画書 現場代理人 受注者 工事着手前 発注者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -50967,7 +50967,7 @@
       </c>
       <c r="W527" t="inlineStr">
         <is>
-          <t>電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="W528" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する「基礎的電気通信役務の提供」及び「利用の公平」|電気通信事業法に規定する「基礎的電気通信役務の提供」及び「利用の公平」 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,基礎的電気通信役務|基礎的電気通信役務 ユニバーサルサービス 提供義務 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51149,7 +51149,7 @@
       </c>
       <c r="W529" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する「工事担任者資格者証」|電気通信事業法に規定する「工事担任者資格者証」 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51238,7 +51238,7 @@
       </c>
       <c r="W530" t="inlineStr">
         <is>
-          <t>電気通信事業法に規定する「端末設備の接続の技術基準」又は「端末設備の接続の検査」|電気通信事業法に規定する「端末設備の接続の技術基準」又は「端末設備の接続の検査」 工事担任者,電気通信事業者|電気通信事業者 法規 工事担任者,電気通信回線設備|電気通信回線設備 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51329,7 +51329,7 @@
       </c>
       <c r="W531" t="inlineStr">
         <is>
-          <t>電気通信事業法|電気通信事業法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51415,7 +51415,7 @@
       </c>
       <c r="W532" t="inlineStr">
         <is>
-          <t>工事担任者規則に規定する「資格者証の種類及び工事の範囲」|工事担任者規則に規定する「資格者証の種類及び工事の範囲」 工事担任者</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51504,7 +51504,7 @@
       </c>
       <c r="W533" t="inlineStr">
         <is>
-          <t>工事担任者|工事担任者 資格 法規</t>
+          <t>工事担任者規則|工事担任者規則 資格 工事範囲 法規 工事担任者,資格者証の再交付|資格者証の再交付 規則 申請 総務大臣 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51595,7 +51595,7 @@
       </c>
       <c r="W534" t="inlineStr">
         <is>
-          <t>移動電話端末|移動電話端末 技術基準 工事担任者</t>
+          <t>技術基準適合認定|技術基準適合認定 端末設備 法規 表示 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51689,7 +51689,7 @@
       </c>
       <c r="W535" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="W536" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信事業法|電気通信事業法 法規 端末設備 接続 工事担任者,電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,有線電気通信法|有線電気通信法 目的 設備検査 総務大臣 法規 工事担任者,責任の分界・分界点|責任の分界・分界点 端末設備 事業用 切り離し 工事担任者,重要通信・緊急通信|重要通信・緊急通信 電気通信事業法 災害 優先 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51872,7 +51872,7 @@
       </c>
       <c r="W537" t="inlineStr">
         <is>
-          <t>用語|電気通信用語 工事担任者</t>
+          <t>電気通信回線設備|電気通信回線設備 法規 端末設備 接続 工事担任者,専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="W538" t="inlineStr">
         <is>
-          <t>音響衝撃|音響衝撃 工事担任者</t>
+          <t>端末設備等規則|端末設備等規則 技術基準 法規 接続条件 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52054,7 +52054,7 @@
       </c>
       <c r="W539" t="inlineStr">
         <is>
-          <t>「絶縁抵抗等」|「絶縁抵抗等」 工事担任者,端末設備等規則|端末設備等規則 工事担任者</t>
+          <t>端末設備等規則|端末設備等規則 技術基準 法規 接続条件 工事担任者,絶縁抵抗測定 (端末設備)|絶縁抵抗測定 (端末設備) 直流200V 1メガオーム 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52148,7 +52148,7 @@
       </c>
       <c r="W540" t="inlineStr">
         <is>
-          <t>配線設備等の評価雑音電力|評価雑音電力 配線設備 工事担任者</t>
+          <t>評価雑音電力|評価雑音電力 聴覚率 実効値 端末設備 法規 工事担任者,端末設備等規則|端末設備等規則 技術基準 法規 接続条件 工事担任者,端末設備の安全性|端末設備の安全性 評価雑音電力 安全 法規 工事担任者,端末設備の安全基準|端末設備の安全基準 評価雑音電力 過大音響 漏えい電流 法規 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52239,7 +52239,7 @@
       </c>
       <c r="W541" t="inlineStr">
         <is>
-          <t>「端末設備内において電波を使用する端末設備」|「端末設備内において電波を使用する端末設備」 工事担任者</t>
+          <t>端末設備内電波使用 空き状態確認|端末設備内電波使用 空き状態確認 周波数 通信路設定 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52328,7 +52328,7 @@
       </c>
       <c r="W542" t="inlineStr">
         <is>
-          <t>アナログ電話端末|アナログ電話端末 技術基準 工事担任者,総合デジタル通信端末|総合デジタル通信端末 ISDN 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52415,7 +52415,7 @@
       </c>
       <c r="W543" t="inlineStr">
         <is>
-          <t>インターネットプロトコル移動電話端末の「基本的機能」及び「発信の機能」|インターネットプロトコル移動電話端末の「基本的機能」及び「発信の機能」 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52506,7 +52506,7 @@
       </c>
       <c r="W544" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末の「電気的条件等」|専用通信回線設備等端末の「電気的条件等」 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者,分界点の接続条件 (電気的・光学的)|分界点の接続条件 (電気的・光学的) 端末設備 切り離し 規則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="W545" t="inlineStr">
         <is>
-          <t>漏話|漏話 クロストーク 工事担任者,専用通信回線|専用通信回線設備等端末 工事担任者</t>
+          <t>専用通信回線設備|専用通信回線設備 特定利用者 専用役務 電気通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52694,7 +52694,7 @@
       </c>
       <c r="W546" t="inlineStr">
         <is>
-          <t>アナログ電話端末等の選択信号における押しボタンダイヤル信号の条件|アナログ電話端末等の選択信号における押しボタンダイヤル信号の条件 工事担任者</t>
+          <t>アナログ電話端末規定|アナログ電話端末規定 端末設備 法規 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52785,7 +52785,7 @@
       </c>
       <c r="W547" t="inlineStr">
         <is>
-          <t>有線電気通信設備令に規定する「架空電線と他人の設置した架空電線等との関係」|有線電気通信設備令に規定する「架空電線と他人の設置した架空電線等との関係」 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52879,7 +52879,7 @@
       </c>
       <c r="W548" t="inlineStr">
         <is>
-          <t>光ファイバ|光ファイバ 工事担任者,有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -52970,7 +52970,7 @@
       </c>
       <c r="W549" t="inlineStr">
         <is>
-          <t>有線電気通信|有線電気通信法 工事担任者</t>
+          <t>電気通信法規|電気通信法規 解説 工事担任者</t>
         </is>
       </c>
     </row>
@@ -53061,7 +53061,7 @@
       </c>
       <c r="W550" t="inlineStr">
         <is>
-          <t>不正アクセス行為|不正アクセス行為 工事担任者,アクセス制御|アクセス制御 工事担任者,識別符号|識別符号 アクセス制御 工事担任者,不正アクセス行為の禁止|不正アクセス禁止法 工事担任者</t>
+          <t>不正アクセス対策|不正アクセス対策 ファイアウォール 侵入検知 セキュリティ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -53152,7 +53152,7 @@
       </c>
       <c r="W551" t="inlineStr">
         <is>
-          <t>電子署名|電子署名 工事担任者,電磁的記録|電磁的記録 電子署名法 工事担任者,認証業務|認証業務 電子署名法 工事担任者</t>
+          <t>デジタル署名|デジタル署名 公開鍵 改ざん検知 PKI 工事担任者</t>
         </is>
       </c>
     </row>
